--- a/output/pdf_financials_xlsx/ARGL.xlsx
+++ b/output/pdf_financials_xlsx/ARGL.xlsx
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.915281</v>
+        <v>2.481491</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
@@ -3321,7 +3321,11 @@
           <t>Reserve for warrants (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ARGL.xlsx
+++ b/output/pdf_financials_xlsx/ARGL.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004698</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.023039</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.320546</v>
+        <v>-0.325244</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.269862</v>
+        <v>-4.292901</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.320546</v>
+        <v>-0.325244</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.269862</v>
+        <v>-4.292901</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.460657</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.420653</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.460657</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.420653</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.528629</v>
+        <v>0.067972</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.385202</v>
+        <v>0.964549</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARGL.xlsx
+++ b/output/pdf_financials_xlsx/ARGL.xlsx
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.028093</v>
+        <v>0.054943</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.121529</v>
+        <v>0.3656</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.028093</v>
+        <v>0.054943</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.121529</v>
+        <v>0.3656</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -1031,10 +1031,8 @@
       <c r="C34" s="3" t="n">
         <v>2.420653</v>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" s="3" t="n">
+        <v>2.420653</v>
       </c>
     </row>
     <row r="35">
@@ -1049,10 +1047,8 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1067,10 +1063,8 @@
       <c r="C36" s="3" t="n">
         <v>2.420653</v>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D36" s="3" t="n">
+        <v>2.420653</v>
       </c>
     </row>
     <row r="37">
@@ -1085,10 +1079,8 @@
       <c r="C37" s="3" t="n">
         <v>0.112208</v>
       </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D37" s="3" t="n">
+        <v>0.112208</v>
       </c>
     </row>
     <row r="38">
@@ -1103,10 +1095,8 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1121,10 +1111,8 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1139,10 +1127,8 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1157,10 +1143,8 @@
       <c r="C41" s="3" t="n">
         <v>0.112208</v>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D41" s="3" t="n">
+        <v>0.112208</v>
       </c>
     </row>
     <row r="42">
@@ -1175,10 +1159,8 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1193,10 +1175,8 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1211,10 +1191,8 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1229,10 +1207,8 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1247,10 +1223,8 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1265,10 +1239,8 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1283,10 +1255,8 @@
       <c r="C48" s="3" t="n">
         <v>0.964549</v>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D48" s="3" t="n">
+        <v>0.964549</v>
       </c>
     </row>
     <row r="49">
@@ -1301,10 +1271,8 @@
       <c r="C49" s="3" t="n">
         <v>3.49741</v>
       </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D49" s="3" t="n">
+        <v>3.49741</v>
       </c>
     </row>
     <row r="50">
@@ -1319,10 +1287,8 @@
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1337,10 +1303,8 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1355,10 +1319,8 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1373,10 +1335,8 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1391,10 +1351,8 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1431,10 +1389,8 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1449,10 +1405,8 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1467,10 +1421,8 @@
       <c r="C58" s="3" t="n">
         <v>0.989868</v>
       </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D58" s="3" t="n">
+        <v>0.989868</v>
       </c>
     </row>
     <row r="59">
@@ -1485,10 +1437,8 @@
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1503,10 +1453,8 @@
       <c r="C60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1521,10 +1469,8 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1539,10 +1485,8 @@
       <c r="C62" s="3" t="n">
         <v>0.989868</v>
       </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D62" s="3" t="n">
+        <v>0.989868</v>
       </c>
     </row>
     <row r="63">
@@ -1557,10 +1501,8 @@
       <c r="C63" s="3" t="n">
         <v>4.487278</v>
       </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D63" s="3" t="n">
+        <v>4.487278</v>
       </c>
     </row>
     <row r="64">
@@ -1570,15 +1512,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.085215</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.050894</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.044815</v>
       </c>
     </row>
     <row r="65">
@@ -1593,10 +1533,8 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1611,10 +1549,8 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1627,12 +1563,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.118661</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.08684699999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1647,10 +1581,8 @@
       <c r="C68" s="3" t="n">
         <v>0.169555</v>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D68" s="3" t="n">
+        <v>0.169555</v>
       </c>
     </row>
     <row r="69">
@@ -1665,10 +1597,8 @@
       <c r="C69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1683,10 +1613,8 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1701,10 +1629,8 @@
       <c r="C71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1719,10 +1645,8 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1737,10 +1661,8 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1755,10 +1677,8 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1773,10 +1693,8 @@
       <c r="C75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1813,10 +1731,8 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1831,10 +1747,8 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1849,10 +1763,8 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1889,10 +1801,8 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1907,10 +1817,8 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1925,10 +1833,8 @@
       <c r="C83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1943,10 +1849,8 @@
       <c r="C84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1961,10 +1865,8 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2001,10 +1903,8 @@
       <c r="C87" s="3" t="n">
         <v>0.187202</v>
       </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D87" s="3" t="n">
+        <v>0.187202</v>
       </c>
     </row>
     <row r="88">
@@ -2019,10 +1919,8 @@
       <c r="C88" s="3" t="n">
         <v>6.349685</v>
       </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D88" s="3" t="n">
+        <v>6.349685</v>
       </c>
     </row>
     <row r="89">
@@ -2037,10 +1935,8 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2073,10 +1969,8 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2091,10 +1985,8 @@
       <c r="C92" s="3" t="n">
         <v>2.481491</v>
       </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D92" s="3" t="n">
+        <v>2.481491</v>
       </c>
     </row>
     <row r="93">
@@ -2109,10 +2001,8 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2127,10 +2017,8 @@
       <c r="C94" s="3" t="n">
         <v>4.300076</v>
       </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D94" s="3" t="n">
+        <v>4.300076</v>
       </c>
     </row>
     <row r="95">
@@ -2145,10 +2033,8 @@
       <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2163,10 +2049,8 @@
       <c r="C96" s="3" t="n">
         <v>4.300076</v>
       </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D96" s="3" t="n">
+        <v>4.300076</v>
       </c>
     </row>
     <row r="97">
@@ -2181,10 +2065,8 @@
       <c r="C97" s="3" t="n">
         <v>0.958281613040244</v>
       </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D97" s="3" t="n">
+        <v>0.958281613040244</v>
       </c>
     </row>
     <row r="98">
@@ -2224,10 +2106,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2242,10 +2122,8 @@
       <c r="C101" s="3" t="n">
         <v>-0.107646</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>-0.107646</v>
       </c>
     </row>
     <row r="102">
@@ -2260,10 +2138,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2278,10 +2154,8 @@
       <c r="C103" s="3" t="n">
         <v>-0.959549</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>-0.959549</v>
       </c>
     </row>
     <row r="104">
@@ -2296,10 +2170,8 @@
       <c r="C104" s="3" t="n">
         <v>0.08434</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.08434</v>
       </c>
     </row>
     <row r="105">
@@ -2314,10 +2186,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2332,10 +2202,8 @@
       <c r="C106" s="3" t="n">
         <v>-0.982855</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>-0.982855</v>
       </c>
     </row>
     <row r="107">
@@ -2350,10 +2218,8 @@
       <c r="C107" s="3" t="n">
         <v>1.182339</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>1.182339</v>
       </c>
     </row>
     <row r="108">
@@ -2368,10 +2234,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2386,10 +2250,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2404,10 +2266,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2422,10 +2282,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2440,10 +2298,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2458,10 +2314,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2476,10 +2330,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2494,10 +2346,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2512,10 +2362,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2530,10 +2378,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2548,10 +2394,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2566,10 +2410,8 @@
       <c r="C119" s="3" t="n">
         <v>-0.247368</v>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>-0.247368</v>
       </c>
     </row>
     <row r="120">
@@ -2584,10 +2426,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2602,10 +2442,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2620,10 +2458,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2638,10 +2474,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2656,10 +2490,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2674,10 +2506,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2692,10 +2522,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2732,10 +2560,8 @@
       <c r="C128" s="3" t="n">
         <v>-0.200845</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2750,10 +2576,8 @@
       <c r="C129" s="3" t="n">
         <v>6.19677</v>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>6.19677</v>
       </c>
     </row>
     <row r="130">
@@ -2768,10 +2592,8 @@
       <c r="C130" s="3" t="n">
         <v>0.460657</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.460657</v>
       </c>
     </row>
     <row r="131">
@@ -2786,10 +2608,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2804,10 +2624,8 @@
       <c r="C132" s="3" t="n">
         <v>1.959996</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>1.959996</v>
       </c>
     </row>
     <row r="133">
@@ -2822,10 +2640,8 @@
       <c r="C133" s="3" t="n">
         <v>2.420653</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>2.420653</v>
       </c>
     </row>
     <row r="134">
@@ -2840,10 +2656,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2858,10 +2672,8 @@
       <c r="C135" s="3" t="n">
         <v>-3.069523</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-3.069523</v>
       </c>
     </row>
   </sheetData>
@@ -2875,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2927,23 +2739,33 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>February 28, 2025 February</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>2.9e-05</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash 1,032,883</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>2.420653</v>
       </c>
     </row>
     <row r="3">
@@ -2959,24 +2781,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Accounts receivable 77,265</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.460657</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>2.420653</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.112208</v>
       </c>
     </row>
     <row r="4">
@@ -2992,24 +2816,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Prepaid expenses (Note 4) 31,262</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AccountsReceivable</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.004562</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.112208</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.964549</v>
       </c>
     </row>
     <row r="5">
@@ -3025,24 +2851,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prepaid expenses (Note 4)</t>
+          <t>Total Current Assets 1,141,410</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0.964549</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.49741</v>
       </c>
     </row>
     <row r="6">
@@ -3058,22 +2886,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Deferred listing costs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="5" t="n">
-        <v>0.062972</v>
+          <t>Exploration and evaluation assets (Note 5) 978,223</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>0.989868</v>
       </c>
     </row>
     <row r="7">
@@ -3089,24 +2921,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Total Current Assets</t>
+          <t>Total Assets 2,119,633</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.533191</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>3.49741</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>4.487278</v>
       </c>
     </row>
     <row r="8">
@@ -3117,29 +2951,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets (Note 5)</t>
+          <t>Accounts payable and accrued liabilities (Note 6) 131,662</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.989868</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.169555</v>
       </c>
     </row>
     <row r="9">
@@ -3150,29 +2986,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.551191</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>4.487278</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Flow-through share liability (Note 7) 35,814</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.017647</v>
       </c>
     </row>
     <row r="10">
@@ -3188,24 +3022,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 6)</t>
+          <t>Total Liabilities 167,476</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0.085215</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.169555</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.187202</v>
       </c>
     </row>
     <row r="11">
@@ -3216,27 +3052,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Flow-through share liability (Note 7)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Share capital (Note 8) 11,086,353</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.017647</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.349685</v>
       </c>
     </row>
     <row r="12">
@@ -3247,29 +3087,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
+          <t>Reserve for warrants (Note 8) 2,162,974</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.085215</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.187202</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.56621</v>
       </c>
     </row>
     <row r="13">
@@ -3285,24 +3127,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Share capital (Note 8)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.7865220000000001</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>6.349685</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Reserve for restricted share units (Note 8) 90,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.059308</v>
       </c>
     </row>
     <row r="14">
@@ -3318,7 +3158,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reserve for warrants (Note 8)</t>
+          <t>Contributed surplus (Note 8) -</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3331,13 +3171,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>1.56621</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.915281</v>
       </c>
     </row>
     <row r="15">
@@ -3353,7 +3193,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reserve for restricted share units (Note 8)</t>
+          <t>Accumulated deficit (11,387,170)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3362,13 +3202,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>0.059308</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-4.590408</v>
       </c>
     </row>
     <row r="16">
@@ -3384,12 +3224,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contributed surplus (Note 8)</t>
+          <t>Total Shareholders' Equity 1,952,157</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3397,13 +3237,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>0.915281</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>4.300076</v>
       </c>
     </row>
     <row r="17">
@@ -3419,24 +3259,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Total Liabilities and Shareholders' Equity 2,119,633</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>-0.320546</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>-4.590408</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.487278</v>
       </c>
     </row>
     <row r="18">
@@ -3452,24 +3294,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Total Shareholders' Equity</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0.465976</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>4.300076</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Nature of operations and going concern (Note</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1e-06</v>
       </c>
     </row>
     <row r="19">
@@ -3485,81 +3325,73 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders' Equity</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0.551191</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>4.487278</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Commitments and contingencies (Note</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2023 (Date of</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>February 28, 2025</t>
+          <t>Subsequent events (Note</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>2.9e-05</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Operating Activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss for the Year</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>February 28, 2025 February</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" s="5" t="n">
-        <v>-0.320546</v>
+        <v>0.002024</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-4.269862</v>
+        <v>2.9e-05</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3570,31 +3402,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8)</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.460657</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1.182339</v>
+        <v>2.420653</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3605,27 +3435,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Impairment of mineral property (Note 5)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.004562</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.018</v>
+        <v>0.112208</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3636,29 +3468,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Operating Activities total</t>
+          <t>Prepaid expenses (Note 4)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.320546</v>
+        <v>0.005</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-3.069523</v>
+        <v>0.964549</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3669,29 +3501,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Deferred listing costs</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>-0.959549</v>
+        <v>0.062972</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3702,25 +3532,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deferred listing costs</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>-0.062972</v>
+        <v>0.533191</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.062972</v>
+        <v>3.49741</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3731,29 +3565,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Exploration and evaluation assets (Note 5)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-0.004562</v>
+        <v>0.018</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.107646</v>
+        <v>0.989868</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3764,29 +3598,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.085215</v>
+        <v>0.551191</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.08434</v>
+        <v>4.487278</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3797,29 +3631,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash Flows used in Operating Activities</t>
+          <t>Accounts payable and accrued liabilities (Note 6)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-0.307865</v>
+        <v>0.085215</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-3.989406</v>
+        <v>0.169555</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3830,25 +3664,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Payments for E&amp;E Assets</t>
+          <t>Flow-through share liability (Note 7)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>-0.018</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.247368</v>
+        <v>0.017647</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3859,29 +3695,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash Flows used in Investing Activities</t>
+          <t>Total Liabilities</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.085215</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.247368</v>
+        <v>0.187202</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3892,25 +3728,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Private Placement Proceeds (Note 8)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Share capital (Note 8)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>0.797082</v>
+        <v>0.7865220000000001</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>5.133248</v>
+        <v>6.349685</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3921,29 +3761,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 8)</t>
+          <t>Reserve for warrants (Note 8)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>-0.01056</v>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.200845</v>
+        <v>1.56621</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3954,17 +3796,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds from warrant exercise (Note 8)</t>
+          <t>Reserve for restricted share units (Note 8)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3974,7 +3816,7 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1.264367</v>
+        <v>0.059308</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3985,29 +3827,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash Flows provided by Financing Activities</t>
+          <t>Contributed surplus (Note 8)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.7865220000000001</v>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>6.19677</v>
+        <v>0.915281</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4018,29 +3862,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Increase in Cash</t>
+          <t>Accumulated deficit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.460657</v>
+        <v>-0.320546</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1.959996</v>
+        <v>-4.590408</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4051,31 +3895,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash, beginning of Year</t>
+          <t>Total Shareholders' Equity</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.465976</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.460657</v>
+        <v>4.300076</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4086,29 +3928,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash, end of Year</t>
+          <t>Total Liabilities and Shareholders' Equity</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.460657</v>
+        <v>0.551191</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2.420653</v>
+        <v>4.487278</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4119,17 +3961,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Professional fees (Note 9) 271,591</t>
+          <t>Net loss and comprehensive loss for the Year (7,949,475)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -4144,23 +3986,23 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.211489</v>
+        <v>-4.269862</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Consulting and director fees (Note 9) 172,623</t>
+          <t>Premium on flow-through shares (Note 7) (109,275)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -4174,27 +4016,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>0.244071</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Advertising and promotional expenses 2,511,568</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Share-based compensation (Note 8) 879,382</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4206,23 +4054,23 @@
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.534806</v>
+        <v>1.182339</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>General and administrative expenses 85,184</t>
+          <t>Impairment of mineral property (Note 5) 133,899</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4237,57 +4085,61 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.033275</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 5) 3,884,632</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating Activities total</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-0.320546</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>-3.069523</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.7669820000000001</v>
+        <v>-3.069523</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Filing fees 81,174</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Prepaid expenses 933,287</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4299,23 +4151,23 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.121529</v>
+        <v>-0.959549</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salaries and wages 26,730</t>
+          <t>Deferred listing costs -</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4330,26 +4182,30 @@
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.024836</v>
+        <v>0.062972</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8 and 9) 879,382</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Accounts receivable 34,943</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4361,26 +4217,30 @@
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.182339</v>
+        <v>-0.107646</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Loss before Other Items (7,912,884)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (37,893)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -4392,23 +4252,23 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-4.119327</v>
+        <v>0.08434</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Premium on flow-through shares (Note 7) 109,275</t>
+          <t>Cash Flows used in Operating Activities (6,115,132)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4422,26 +4282,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="5" t="n">
+        <v>-3.989406</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Interest income 18,589</t>
+          <t>Payments for E&amp;E Assets (Note 5) (34,254)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4456,26 +4314,30 @@
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.023039</v>
+        <v>-0.247368</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Impairment of mineral property (Note 5) (133,899)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Cash Flows used in Investing Activities (34,254)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -4487,23 +4349,23 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.247368</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Listing costs (14,802)</t>
+          <t>Private Placement Proceeds (Note 8) 3,812,800</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4518,23 +4380,23 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.139231</v>
+        <v>5.133248</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (15,754)</t>
+          <t>Share issuance costs (Note 8) (208,407)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4549,23 +4411,23 @@
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.016343</v>
+        <v>-0.200845</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Total Other Expenses (36,591)</t>
+          <t>Proceeds from warrant exercise (Note 8) 1,025,223</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4580,23 +4442,23 @@
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.150535</v>
+        <v>1.264367</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss (7,949,475)</t>
+          <t>Proceeds from option exercise (Note 8) 132,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4610,27 +4472,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>-4.269862</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 8) 9,826,214</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Cash Flows provided by Financing Activities 4,761,616</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -4642,23 +4510,23 @@
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>5.720606</v>
+        <v>6.19677</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Net Loss per Share</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 8)i (0.81)</t>
+          <t>(Decrease) Increase in Cash (1,387,770)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4673,26 +4541,30 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-7.5e-07</v>
+        <v>1.959996</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Net Loss per Share</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>(i) Adjusted for 5:1 share consolidation effective May 21, 2026 (Notes 8,</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Cash, beginning of Year 2,420,653</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -4704,26 +4576,30 @@
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>0.460657</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Balance, February 29, 2024 4,060,820 786,522 - - - (320,546)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Cash, end of Year 1,032,883</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -4735,97 +4611,99 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.465976</v>
+        <v>2.420653</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>2023 (Date of</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Private placements (Note 8) 2,237,279 3,487,840 1,645,408 - - -</t>
+          <t>February 28, 2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>5.133248</v>
+      <c r="E59" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unit issuance cost - (168,977) (31,868) - - -</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.200845</v>
+          <t>Net loss for the Year</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-0.320546</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-4.269862</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Broker warrants issued - (52,454) 52,454 - - -</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Share-based compensation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" s="5" t="n">
+        <v>1.182339</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4836,17 +4714,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Flow-through liability premium - (17,647) - - - -</t>
+          <t>Impairment of mineral property (Note 5)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4855,103 +4733,103 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.017647</v>
+      <c r="F62" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Issuance of shares on Property Option (Note 5, 8) 210,000 742,500 - - - -</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.7425</v>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-0.959549</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Issuance of shares on Warrants exercise (Note 8) 1,477,233 1,364,151 (99,784) - - -</t>
+          <t>Deferred listing costs</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>1.264367</v>
+      <c r="E64" s="5" t="n">
+        <v>-0.062972</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.062972</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Issuance of shares on RSUs exercise (Note 8) 45,000 207,750 - (207,750) - -</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>-0.004562</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-0.107646</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4962,203 +4840,207 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8) - - - 267,058 915,281 -</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>1.182339</v>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.085215</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.08434</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - (4,269,862)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>-4.269862</v>
+          <t>Cash Flows used in Operating Activities</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>-0.307865</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>-3.989406</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Balance, February 28, 2025 8,030,332 6,349,685 1,566,210 59,308 915,281 (4,590,408)</t>
+          <t>Payments for E&amp;E Assets</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>4.300076</v>
+      <c r="E68" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>-0.247368</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Private placements (Note 8) 2,001,732 2,980,791 784,001 - - -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>3.764792</v>
+          <t>Cash Flows used in Investing Activities</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.247368</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cash issuance cost (Note 8) - (164,788) (44,614) - - -</t>
+          <t>Private Placement Proceeds (Note 8)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>-0.209402</v>
+      <c r="E70" s="5" t="n">
+        <v>0.797082</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>5.133248</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Broker warrants issued (Note 8) - (54,187) 103,190 - - -</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>0.049003</v>
+          <t>Share issuance costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.01056</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.200845</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Flow-through liability premium (Note 7, 8) - (127,442) - - - -</t>
+          <t>Proceeds from warrant exercise (Note 8)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5167,103 +5049,109 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>-0.127442</v>
+      <c r="F72" s="5" t="n">
+        <v>1.264367</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Issuance of shares on Property Option (Note 5, 8) 32,000 88,000 - - - -</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0.08799999999999999</v>
+          <t>Cash Flows provided by Financing Activities</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.7865220000000001</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>6.19677</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Issuance of shares on Warrants exercise (Note 8) 757,566 1,271,036 (245,813) - - -</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>1.025223</v>
+          <t>Increase in Cash</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0.460657</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>1.959996</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Issuance of shares on RSUs exercise (Note 8) 220,000 520,000 - (520,000) - -</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Cash, beginning of Year</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F75" s="5" t="n">
+        <v>0.460657</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5274,32 +5162,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Issuance of shares on Options exercise (Note 8) 60,000 223,258 - - (91,258) -</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.132</v>
+          <t>Cash, end of Year</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.460657</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>2.420653</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5310,12 +5200,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8) - - - 550,692 328,690 -</t>
+          <t>Professional fees (Note 9) 271,591</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5330,7 +5220,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.879382</v>
+        <v>0.211489</v>
       </c>
     </row>
     <row r="78">
@@ -5341,12 +5231,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cancellation of Options (Note 8) - - - - (1,152,713) 1,152,713</t>
+          <t>Consulting and director fees (Note 9) 172,623</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -5360,10 +5250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" s="5" t="n">
+        <v>0.244071</v>
       </c>
     </row>
     <row r="79">
@@ -5374,12 +5262,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - (7,949,475)</t>
+          <t>Advertising and promotional expenses 2,511,568</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -5394,7 +5282,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-7.949475</v>
+        <v>1.534806</v>
       </c>
     </row>
     <row r="80">
@@ -5405,12 +5293,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Balance, February 28, 2026 11,101,630 11,086,353 2,162,974 90,000 - (11,387,170)</t>
+          <t>General and administrative expenses 85,184</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -5425,7 +5313,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1.952157</v>
+        <v>0.033275</v>
       </c>
     </row>
     <row r="81">
@@ -5436,25 +5324,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2023 (Date of</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>February 28, 2025</t>
+          <t>Exploration expenditures (Note 5) 3,884,632</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>2.9e-05</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.7669820000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5470,24 +5360,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Professional fees (note 9)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0.08989999999999999</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0.211489</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Filing fees 81,174</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.121529</v>
       </c>
     </row>
     <row r="83">
@@ -5503,20 +5391,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Consulting and director fees (Note 9)</t>
+          <t>Salaries and wages 26,730</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.02685</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.244071</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.024836</v>
       </c>
     </row>
     <row r="84">
@@ -5532,7 +5422,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Advertising and promotional expenses</t>
+          <t>Share-based compensation (Note 8 and 9) 879,382</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -5541,13 +5431,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>1.534806</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.182339</v>
       </c>
     </row>
     <row r="85">
@@ -5563,24 +5453,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.001204</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.033275</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss before Other Items (7,912,884)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-4.119327</v>
       </c>
     </row>
     <row r="86">
@@ -5591,20 +5479,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 5)</t>
+          <t>Premium on flow-through shares (Note 7) 109,275</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>0.175983</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0.7669820000000001</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5620,29 +5512,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>0.028093</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>0.121529</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income 18,589</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.023039</v>
       </c>
     </row>
     <row r="88">
@@ -5653,29 +5543,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Salaries and wages (Note 9)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>0.003214</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>0.024836</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Impairment of mineral property (Note 5) (133,899)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.018</v>
       </c>
     </row>
     <row r="89">
@@ -5686,12 +5574,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8 and 9)</t>
+          <t>Listing costs (14,802)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -5700,13 +5588,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>1.182339</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.139231</v>
       </c>
     </row>
     <row r="90">
@@ -5717,29 +5605,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Loss before Other Items</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>-0.325244</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>-4.119327</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange loss (15,754)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-0.016343</v>
       </c>
     </row>
     <row r="91">
@@ -5755,24 +5641,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>0.004698</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>0.023039</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Other Expenses (36,591)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.150535</v>
       </c>
     </row>
     <row r="92">
@@ -5788,7 +5672,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Impairment of mineral property (Note 5)</t>
+          <t>Net loss and comprehensive loss (7,949,475)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5797,13 +5681,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-4.269862</v>
       </c>
     </row>
     <row r="93">
@@ -5814,12 +5698,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>i</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Listing costs</t>
+          <t>Basic and diluted (Note 8) 9,826,214</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -5828,13 +5712,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>-0.139231</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>5.720606</v>
       </c>
     </row>
     <row r="94">
@@ -5845,31 +5729,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Net Loss per Share</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Basic and diluted (Note 8)i (0.81)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>-0.016343</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-7.5e-07</v>
       </c>
     </row>
     <row r="95">
@@ -5880,29 +5760,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Net Loss per Share</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Total Other Income (Expenses)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>0.004698</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.150535</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>(i) Adjusted for 5:1 share consolidation effective May 21, 2026 (Notes 8,</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="96">
@@ -5913,29 +5791,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>-0.320546</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>-4.269862</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, February 29, 2024 4,060,820 786,522 - - - (320,546)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.465976</v>
       </c>
     </row>
     <row r="97">
@@ -5946,25 +5822,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Outstanding Shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 8)</t>
+          <t>Private placements (Note 8) 2,237,279 3,487,840 1,645,408 - - -</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>13.821769</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>28.603028</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>5.133248</v>
       </c>
     </row>
     <row r="98">
@@ -5975,29 +5853,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Net Loss per Share</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 8)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>-1.5e-07</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unit issuance cost - (168,977) (31,868) - - -</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.200845</v>
       </c>
     </row>
     <row r="99">
@@ -6013,7 +5889,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Balance, March 16, 2023 - - - - -</t>
+          <t>Broker warrants issued - (52,454) 52,454 - - -</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -6046,22 +5922,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Private placements - net (Note 8) 20,304,098 786,522 - - -</t>
+          <t>Flow-through liability premium - (17,647) - - - -</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>0.7865220000000001</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>-0.017647</v>
       </c>
     </row>
     <row r="101">
@@ -6077,24 +5953,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Net loss for the period - - - - -</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>-0.320546</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>-0.320546</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issuance of shares on Property Option (Note 5, 8) 210,000 742,500 - - - -</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.7425</v>
       </c>
     </row>
     <row r="102">
@@ -6110,20 +5984,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Balance, February 29, 2024 20,304,098 786,522 - - -</t>
+          <t>Issuance of shares on Warrants exercise (Note 8) 1,477,233 1,364,151 (99,784) - - -</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" s="5" t="n">
-        <v>0.465976</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>-0.320546</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>1.264367</v>
       </c>
     </row>
     <row r="103">
@@ -6139,12 +6015,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Private placements (Note 8) 11,186,395 3,487,840 1,645,408 - -</t>
+          <t>Issuance of shares on RSUs exercise (Note 8) 45,000 207,750 - (207,750) - -</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>5.133248</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6170,22 +6048,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cash issuance cost - (168,977) (31,868) - -</t>
+          <t>Share-based compensation (Note 8) - - - 267,058 915,281 -</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
-        <v>-0.200845</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="5" t="n">
+        <v>1.182339</v>
       </c>
     </row>
     <row r="105">
@@ -6201,7 +6079,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Broker warrants issued - (52,454) 52,454 - -</t>
+          <t>Net loss and comprehensive loss for the year - - - - - (4,269,862)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -6215,10 +6093,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="5" t="n">
+        <v>-4.269862</v>
       </c>
     </row>
     <row r="106">
@@ -6234,22 +6110,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Flow-through liability premium - (17,647) - - -</t>
+          <t>Balance, February 28, 2025 8,030,332 6,349,685 1,566,210 59,308 915,281 (4,590,408)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" s="5" t="n">
-        <v>-0.017647</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="5" t="n">
+        <v>4.300076</v>
       </c>
     </row>
     <row r="107">
@@ -6265,22 +6141,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Issuance of shares on Property Option (Note 5, 8) 1,050,000 742,500 - - -</t>
+          <t>Private placements (Note 8) 2,001,732 2,980,791 784,001 - - -</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>0.7425</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="5" t="n">
+        <v>3.764792</v>
       </c>
     </row>
     <row r="108">
@@ -6296,22 +6172,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Issuance of shares on Warrants exercise (Note 8) 7,386,166 1,364,151 (99,784) - -</t>
+          <t>Cash issuance cost (Note 8) - (164,788) (44,614) - - -</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" s="5" t="n">
-        <v>1.264367</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="5" t="n">
+        <v>-0.209402</v>
       </c>
     </row>
     <row r="109">
@@ -6327,7 +6203,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Issuance of shares on RSUs exercise (Note 8) 225,000 207,750 -</t>
+          <t>Broker warrants issued (Note 8) - (54,187) 103,190 - - -</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -6336,13 +6212,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="5" t="n">
-        <v>-0.20775</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.049003</v>
       </c>
     </row>
     <row r="110">
@@ -6358,22 +6234,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8) - - - 267,058 915,281</t>
+          <t>Flow-through liability premium (Note 7, 8) - (127,442) - - - -</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" s="5" t="n">
-        <v>1.182339</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="5" t="n">
+        <v>-0.127442</v>
       </c>
     </row>
     <row r="111">
@@ -6389,24 +6265,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>-4.269862</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>-4.269862</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issuance of shares on Property Option (Note 5, 8) 32,000 88,000 - - - -</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6422,17 +6296,1223 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>Issuance of shares on Warrants exercise (Note 8) 757,566 1,271,036 (245,813) - - -</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>1.025223</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Issuance of shares on RSUs exercise (Note 8) 220,000 520,000 - (520,000) - -</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Issuance of shares on Options exercise (Note 8) 60,000 223,258 - - (91,258) -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 8) - - - 550,692 328,690 -</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.879382</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cancellation of Options (Note 8) - - - - (1,152,713) 1,152,713</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year - - - - - (7,949,475)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>-7.949475</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Balance, February 28, 2026 11,101,630 11,086,353 2,162,974 90,000 - (11,387,170)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.952157</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2023 (Date of</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>February 28, 2025</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Professional fees (note 9)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.211489</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Consulting and director fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.02685</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.244071</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Advertising and promotional expenses</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>1.534806</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>0.001204</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.033275</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Exploration expenditures (Note 5)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>0.175983</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>0.7669820000000001</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0.028093</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0.121529</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Salaries and wages (Note 9)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.003214</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0.024836</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 8 and 9)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>1.182339</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Loss before Other Items</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>-0.325244</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>-4.119327</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.004698</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.023039</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Impairment of mineral property (Note 5)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Listing costs</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>-0.139231</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>-0.016343</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Total Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0.004698</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>-0.150535</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>-0.320546</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>-4.269862</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Outstanding Shares</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Basic and diluted (Note 8)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>13.821769</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>28.603028</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Net Loss per Share</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Basic and diluted (Note 8)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>-1.5e-07</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Balance, March 16, 2023 - - - - -</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Private placements - net (Note 8) 20,304,098 786,522 - - -</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>0.7865220000000001</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Net loss for the period - - - - -</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>-0.320546</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-0.320546</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Balance, February 29, 2024 20,304,098 786,522 - - -</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" s="5" t="n">
+        <v>0.465976</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.320546</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Private placements (Note 8) 11,186,395 3,487,840 1,645,408 - -</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>5.133248</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Cash issuance cost - (168,977) (31,868) - -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>-0.200845</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Broker warrants issued - (52,454) 52,454 - -</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Flow-through liability premium - (17,647) - - -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>-0.017647</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Issuance of shares on Property Option (Note 5, 8) 1,050,000 742,500 - - -</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" s="5" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Issuance of shares on Warrants exercise (Note 8) 7,386,166 1,364,151 (99,784) - -</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" s="5" t="n">
+        <v>1.264367</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Issuance of shares on RSUs exercise (Note 8) 225,000 207,750 -</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>-0.20775</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 8) - - - 267,058 915,281</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" s="5" t="n">
+        <v>1.182339</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>-4.269862</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>-4.269862</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
           <t>Balance, February 28, 2025 40,151,659 6,349,685 1,566,210 59,308 915,281</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" s="5" t="n">
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
         <v>4.300076</v>
       </c>
-      <c r="F112" s="5" t="n">
+      <c r="F150" s="5" t="n">
         <v>-4.590408</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
